--- a/amostras/principal/P17/matriz_rastreabilidade_P17.xlsx
+++ b/amostras/principal/P17/matriz_rastreabilidade_P17.xlsx
@@ -694,6 +694,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -751,6 +752,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -805,27 +807,28 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
-        </is>
-      </c>
+          <t>Nenhuma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Amostra Não Preenchida</t>
+          <t>Nenhuma / Sem Achados</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Aguardando geração (Passo 1 pendente)</t>
+          <t>Não se aplica (amostra limpa)</t>
         </is>
       </c>
     </row>
@@ -865,6 +868,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -922,6 +926,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -979,6 +984,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1036,6 +1042,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1093,6 +1100,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1150,6 +1158,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1207,6 +1216,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1264,6 +1274,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1321,6 +1332,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1378,6 +1390,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1435,6 +1448,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1492,6 +1506,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Nenhum</t>
